--- a/Sample_1_UPSC_IAS_Coaching.xlsx
+++ b/Sample_1_UPSC_IAS_Coaching.xlsx
@@ -461,11 +461,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -659,7 +661,7 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Test 1</t>
+          <t>Test 1 Name</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -667,124 +669,364 @@
           <t>Prelims Mock 1</t>
         </is>
       </c>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Test 2</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Prelims Mock 2</t>
-        </is>
-      </c>
+          <t>Test 1 Date</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Test 3</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Mains Test Series 1</t>
-        </is>
-      </c>
+          <t>Max Marks - GS Paper 1 (Test 1)</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Test 4</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Mains Test Series 2</t>
-        </is>
-      </c>
+          <t>Max Marks - GS Paper 2 (CSAT) (Test 1)</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>SCORING CONFIG</t>
-        </is>
-      </c>
-      <c r="B22" s="1" t="n"/>
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Max Marks - Essay (Test 1)</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Pass Threshold %</t>
+          <t>Max Marks - Optional Subject (Test 1)</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>45</v>
+        <v>200</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Absent Alert (days)</t>
+          <t>Max Marks - Current Affairs (Test 1)</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>2</v>
+        <v>200</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Drop Alert %</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>15</v>
+          <t>Test 2 Name</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Prelims Mock 2</t>
+        </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Display Marks</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Test 2 Date</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Display Percentage</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
+          <t>Max Marks - GS Paper 1 (Test 2)</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Display Grade</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
+          <t>Max Marks - GS Paper 2 (CSAT) (Test 2)</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>Max Marks - Essay (Test 2)</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Max Marks - Optional Subject (Test 2)</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Max Marks - Current Affairs (Test 2)</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Test 3 Name</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Mains Test Series 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Test 3 Date</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Max Marks - GS Paper 1 (Test 3)</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Max Marks - GS Paper 2 (CSAT) (Test 3)</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Max Marks - Essay (Test 3)</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Max Marks - Optional Subject (Test 3)</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Max Marks - Current Affairs (Test 3)</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Test 4 Name</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Mains Test Series 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Test 4 Date</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Max Marks - GS Paper 1 (Test 4)</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Max Marks - GS Paper 2 (CSAT) (Test 4)</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Max Marks - Essay (Test 4)</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Max Marks - Optional Subject (Test 4)</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Max Marks - Current Affairs (Test 4)</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>SCORING CONFIG</t>
+        </is>
+      </c>
+      <c r="B46" s="1" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Pass Threshold %</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Absent Alert (days)</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Drop Alert %</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Display Marks</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Display Percentage</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Display Grade</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
           <t>Display Pass/Fail</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>

--- a/Sample_1_UPSC_IAS_Coaching.xlsx
+++ b/Sample_1_UPSC_IAS_Coaching.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/a1989/Downloads/files (1)/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/a1989/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{732AE67B-EDE5-8249-A483-95B8252FC4F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18A1894D-111E-6D48-A6BD-43048DDCE6C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="25600" windowHeight="15400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="25600" windowHeight="15400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SETUP" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="135">
   <si>
     <t>INSTITUTION</t>
   </si>
@@ -420,25 +420,13 @@
     <t>The app will read SETUP automatically and validate completeness.</t>
   </si>
   <si>
-    <t>MODE</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Usage Mode</t>
-  </si>
-  <si>
-    <t>institution</t>
-  </si>
-  <si>
     <t>Hakki IAS Academy</t>
   </si>
   <si>
     <t>mentor@hakki.in</t>
   </si>
   <si>
-    <t>Dr. Sandeep Hakki (Mentor)</t>
+    <t>Dr. Sandeep Hakki Malhotra (Mentor)</t>
   </si>
 </sst>
 </file>
@@ -845,7 +833,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -854,191 +842,191 @@
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+    </row>
+    <row r="2" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>135</v>
-      </c>
     </row>
     <row r="3" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="1"/>
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="4" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>136</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1"/>
     </row>
     <row r="7" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>137</v>
+        <v>8</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1"/>
+      <c r="A8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="9" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>11</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="A11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="1"/>
     </row>
     <row r="12" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="1"/>
+      <c r="A13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="14" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>23</v>
-      </c>
+      <c r="A17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="1"/>
     </row>
     <row r="18" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>25</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
     </row>
     <row r="19" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="1"/>
+      <c r="A19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
     </row>
     <row r="20" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
+      </c>
+      <c r="B20" s="2">
+        <v>200</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
     <row r="21" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B21" s="2"/>
+        <v>31</v>
+      </c>
+      <c r="B21" s="2">
+        <v>200</v>
+      </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
     </row>
     <row r="22" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B22" s="2">
         <v>200</v>
       </c>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
     </row>
     <row r="23" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B23" s="2">
         <v>200</v>
       </c>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
     </row>
     <row r="24" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B24" s="2">
         <v>200</v>
@@ -1046,53 +1034,53 @@
     </row>
     <row r="25" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B25" s="2">
-        <v>200</v>
+        <v>35</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26" s="2">
-        <v>200</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B26" s="2"/>
     </row>
     <row r="27" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
+      </c>
+      <c r="B27" s="2">
+        <v>200</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="B28" s="2">
+        <v>200</v>
+      </c>
     </row>
     <row r="29" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B29" s="2">
         <v>200</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B30" s="2">
         <v>200</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B31" s="2">
         <v>200</v>
@@ -1100,37 +1088,37 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B32" s="2">
-        <v>200</v>
+        <v>43</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B33" s="2">
-        <v>200</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="B33" s="2"/>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
+      </c>
+      <c r="B34" s="2">
+        <v>250</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B35" s="2"/>
+        <v>47</v>
+      </c>
+      <c r="B35" s="2">
+        <v>250</v>
+      </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B36" s="2">
         <v>250</v>
@@ -1138,7 +1126,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B37" s="2">
         <v>250</v>
@@ -1146,7 +1134,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B38" s="2">
         <v>250</v>
@@ -1154,37 +1142,37 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B39" s="2">
-        <v>250</v>
+        <v>51</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B40" s="2">
-        <v>250</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="B40" s="2"/>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
+      </c>
+      <c r="B41" s="2">
+        <v>250</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B42" s="2"/>
+        <v>55</v>
+      </c>
+      <c r="B42" s="2">
+        <v>250</v>
+      </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B43" s="2">
         <v>250</v>
@@ -1192,7 +1180,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B44" s="2">
         <v>250</v>
@@ -1200,61 +1188,61 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B45" s="2">
         <v>250</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A46" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B46" s="2">
-        <v>250</v>
-      </c>
+      <c r="A46" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B46" s="1"/>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B47" s="2">
-        <v>250</v>
+        <v>45</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A48" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B48" s="1"/>
+      <c r="A48" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B48" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B49" s="2">
-        <v>45</v>
+        <v>15</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B50" s="2">
-        <v>2</v>
+        <v>63</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B51" s="2">
-        <v>15</v>
+        <v>65</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>64</v>
@@ -1262,31 +1250,15 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A54" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A55" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B7" r:id="rId1" xr:uid="{CC2AD537-ACC6-4846-AA96-E0C7E6F53DDC}"/>
+    <hyperlink ref="B5" r:id="rId1" xr:uid="{A1F08F77-DCC1-DF44-9156-C2A8A453C272}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1409,73 +1381,73 @@
         <v>101</v>
       </c>
       <c r="D2">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="E2">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="F2">
-        <v>85</v>
+        <v>170</v>
       </c>
       <c r="G2">
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="H2">
-        <v>81</v>
+        <v>162</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="K2">
-        <v>85</v>
+        <v>170</v>
       </c>
       <c r="L2">
-        <v>83</v>
+        <v>166</v>
       </c>
       <c r="M2">
-        <v>86</v>
+        <v>172</v>
       </c>
       <c r="N2">
-        <v>85</v>
+        <v>170</v>
       </c>
       <c r="O2">
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="R2">
-        <v>90</v>
+        <v>225</v>
       </c>
       <c r="S2">
-        <v>92</v>
+        <v>230</v>
       </c>
       <c r="T2">
-        <v>89</v>
+        <v>222</v>
       </c>
       <c r="U2">
-        <v>90</v>
+        <v>225</v>
       </c>
       <c r="V2">
-        <v>89</v>
+        <v>222</v>
       </c>
       <c r="W2">
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>92</v>
+        <v>230</v>
       </c>
       <c r="Z2">
-        <v>90</v>
+        <v>225</v>
       </c>
       <c r="AA2">
-        <v>91</v>
+        <v>228</v>
       </c>
       <c r="AB2">
-        <v>90</v>
+        <v>225</v>
       </c>
       <c r="AC2">
-        <v>92</v>
+        <v>230</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -1495,73 +1467,73 @@
         <v>105</v>
       </c>
       <c r="D3">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="E3">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="F3">
-        <v>74</v>
+        <v>148</v>
       </c>
       <c r="G3">
-        <v>72</v>
+        <v>144</v>
       </c>
       <c r="H3">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="K3">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="L3">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="M3">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="N3">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="O3">
-        <v>73</v>
+        <v>146</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="R3">
-        <v>82</v>
+        <v>205</v>
       </c>
       <c r="S3">
-        <v>72</v>
+        <v>180</v>
       </c>
       <c r="T3">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="U3">
-        <v>84</v>
+        <v>210</v>
       </c>
       <c r="V3">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="W3">
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>84</v>
+        <v>210</v>
       </c>
       <c r="Z3">
-        <v>74</v>
+        <v>185</v>
       </c>
       <c r="AA3">
-        <v>78</v>
+        <v>195</v>
       </c>
       <c r="AB3">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="AC3">
-        <v>82</v>
+        <v>205</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -1581,73 +1553,73 @@
         <v>101</v>
       </c>
       <c r="D4">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="E4">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="F4">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="G4">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="H4">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="K4">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="L4">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="M4">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="N4">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="O4">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="R4">
-        <v>75</v>
+        <v>188</v>
       </c>
       <c r="S4">
-        <v>73</v>
+        <v>182</v>
       </c>
       <c r="T4">
-        <v>74</v>
+        <v>185</v>
       </c>
       <c r="U4">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="V4">
-        <v>72</v>
+        <v>180</v>
       </c>
       <c r="W4">
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>85</v>
+        <v>212</v>
       </c>
       <c r="Z4">
-        <v>83</v>
+        <v>208</v>
       </c>
       <c r="AA4">
-        <v>84</v>
+        <v>210</v>
       </c>
       <c r="AB4">
-        <v>82</v>
+        <v>205</v>
       </c>
       <c r="AC4">
-        <v>83</v>
+        <v>208</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -1667,73 +1639,73 @@
         <v>105</v>
       </c>
       <c r="D5">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="E5">
-        <v>72</v>
+        <v>144</v>
       </c>
       <c r="F5">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="G5">
-        <v>74</v>
+        <v>148</v>
       </c>
       <c r="H5">
-        <v>73</v>
+        <v>146</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="K5">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="L5">
-        <v>62</v>
+        <v>124</v>
       </c>
       <c r="M5">
-        <v>63</v>
+        <v>126</v>
       </c>
       <c r="N5">
-        <v>62</v>
+        <v>124</v>
       </c>
       <c r="O5">
-        <v>63</v>
+        <v>126</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="R5">
-        <v>45</v>
+        <v>112</v>
       </c>
       <c r="S5">
-        <v>46</v>
+        <v>115</v>
       </c>
       <c r="T5">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="U5">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="V5">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="W5">
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>35</v>
+        <v>88</v>
       </c>
       <c r="Z5">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="AA5">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="AB5">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="AC5">
-        <v>35</v>
+        <v>88</v>
       </c>
       <c r="AD5">
         <v>0</v>
@@ -1753,73 +1725,73 @@
         <v>101</v>
       </c>
       <c r="D6">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="E6">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F6">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="G6">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="H6">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="K6">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="L6">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="M6">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="N6">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="O6">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="R6">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="S6">
-        <v>47</v>
+        <v>118</v>
       </c>
       <c r="T6">
-        <v>45</v>
+        <v>112</v>
       </c>
       <c r="U6">
-        <v>55</v>
+        <v>138</v>
       </c>
       <c r="V6">
-        <v>52</v>
+        <v>130</v>
       </c>
       <c r="W6">
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>78</v>
+        <v>195</v>
       </c>
       <c r="Z6">
-        <v>75</v>
+        <v>188</v>
       </c>
       <c r="AA6">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="AB6">
-        <v>82</v>
+        <v>205</v>
       </c>
       <c r="AC6">
-        <v>74</v>
+        <v>185</v>
       </c>
       <c r="AD6">
         <v>0</v>
@@ -1839,73 +1811,73 @@
         <v>105</v>
       </c>
       <c r="D7">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="E7">
-        <v>61</v>
+        <v>122</v>
       </c>
       <c r="F7">
-        <v>59</v>
+        <v>118</v>
       </c>
       <c r="G7">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="H7">
-        <v>61</v>
+        <v>122</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="K7">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="L7">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="M7">
-        <v>62</v>
+        <v>124</v>
       </c>
       <c r="N7">
-        <v>61</v>
+        <v>122</v>
       </c>
       <c r="O7">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="R7">
-        <v>62</v>
+        <v>155</v>
       </c>
       <c r="S7">
-        <v>63</v>
+        <v>158</v>
       </c>
       <c r="T7">
-        <v>61</v>
+        <v>152</v>
       </c>
       <c r="U7">
-        <v>62</v>
+        <v>155</v>
       </c>
       <c r="V7">
-        <v>63</v>
+        <v>158</v>
       </c>
       <c r="W7">
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="Z7">
-        <v>58</v>
+        <v>145</v>
       </c>
       <c r="AA7">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="AB7">
-        <v>58</v>
+        <v>145</v>
       </c>
       <c r="AC7">
-        <v>59</v>
+        <v>148</v>
       </c>
       <c r="AD7">
         <v>0</v>
@@ -1925,73 +1897,73 @@
         <v>101</v>
       </c>
       <c r="D8">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="E8">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="F8">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="G8">
-        <v>59</v>
+        <v>118</v>
       </c>
       <c r="H8">
-        <v>61</v>
+        <v>122</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="K8">
-        <v>63</v>
+        <v>126</v>
       </c>
       <c r="L8">
-        <v>63</v>
+        <v>126</v>
       </c>
       <c r="M8">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="N8">
-        <v>63</v>
+        <v>126</v>
       </c>
       <c r="O8">
-        <v>62</v>
+        <v>124</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="R8">
-        <v>68</v>
+        <v>170</v>
       </c>
       <c r="S8">
-        <v>70</v>
+        <v>175</v>
       </c>
       <c r="T8">
-        <v>67</v>
+        <v>168</v>
       </c>
       <c r="U8">
-        <v>71</v>
+        <v>178</v>
       </c>
       <c r="V8">
-        <v>72</v>
+        <v>180</v>
       </c>
       <c r="W8">
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>74</v>
+        <v>185</v>
       </c>
       <c r="Z8">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="AA8">
-        <v>75</v>
+        <v>188</v>
       </c>
       <c r="AB8">
-        <v>74</v>
+        <v>185</v>
       </c>
       <c r="AC8">
-        <v>72</v>
+        <v>180</v>
       </c>
       <c r="AD8">
         <v>0</v>
@@ -2011,73 +1983,73 @@
         <v>105</v>
       </c>
       <c r="D9">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="E9">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="F9">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="G9">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="H9">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="K9">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="L9">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="M9">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="N9">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="O9">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="R9">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="S9">
-        <v>52</v>
+        <v>130</v>
       </c>
       <c r="T9">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="U9">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="V9">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="W9">
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>52</v>
+        <v>130</v>
       </c>
       <c r="Z9">
-        <v>56</v>
+        <v>140</v>
       </c>
       <c r="AA9">
-        <v>45</v>
+        <v>112</v>
       </c>
       <c r="AB9">
-        <v>42</v>
+        <v>105</v>
       </c>
       <c r="AC9">
-        <v>54</v>
+        <v>135</v>
       </c>
       <c r="AD9">
         <v>0</v>
